--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -60,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="109">
   <si>
     <t>#</t>
   </si>
@@ -384,6 +389,9 @@
   </si>
   <si>
     <t>领主宝宝</t>
+  </si>
+  <si>
+    <t>狮王宝宝</t>
   </si>
 </sst>
 </file>
@@ -569,12 +577,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3404,6 +3412,330 @@
         <v>11</v>
       </c>
     </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="1">
+        <v>73</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E78" s="3">
+        <v>5</v>
+      </c>
+      <c r="F78" s="1">
+        <f t="shared" ref="F78:F89" si="2">INT((C78-1)/6)+1101</f>
+        <v>1113</v>
+      </c>
+      <c r="G78" s="1">
+        <v>11</v>
+      </c>
+      <c r="H78" s="1">
+        <v>2</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J78" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="1">
+        <v>74</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E79" s="3">
+        <v>5</v>
+      </c>
+      <c r="F79" s="1">
+        <f t="shared" si="2"/>
+        <v>1113</v>
+      </c>
+      <c r="G79" s="1">
+        <v>11</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J79" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="1">
+        <v>75</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E80" s="3">
+        <v>5</v>
+      </c>
+      <c r="F80" s="1">
+        <f t="shared" si="2"/>
+        <v>1113</v>
+      </c>
+      <c r="G80" s="1">
+        <v>11</v>
+      </c>
+      <c r="H80" s="1">
+        <v>2</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J80" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="1">
+        <v>76</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="2"/>
+        <v>1113</v>
+      </c>
+      <c r="G81" s="1">
+        <v>11</v>
+      </c>
+      <c r="H81" s="1">
+        <v>2</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J81" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="1">
+        <v>77</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="3">
+        <v>5</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="2"/>
+        <v>1113</v>
+      </c>
+      <c r="G82" s="1">
+        <v>11</v>
+      </c>
+      <c r="H82" s="1">
+        <v>2</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J82" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="1">
+        <v>78</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5</v>
+      </c>
+      <c r="F83" s="1">
+        <f t="shared" si="2"/>
+        <v>1113</v>
+      </c>
+      <c r="G83" s="1">
+        <v>11</v>
+      </c>
+      <c r="H83" s="1">
+        <v>2</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J83" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="1">
+        <v>79</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E84" s="3">
+        <v>5</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="G84" s="1">
+        <v>11</v>
+      </c>
+      <c r="H84" s="1">
+        <v>2</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J84" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="1">
+        <v>80</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E85" s="3">
+        <v>5</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="G85" s="1">
+        <v>11</v>
+      </c>
+      <c r="H85" s="1">
+        <v>2</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J85" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
+      <c r="C86" s="1">
+        <v>81</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E86" s="3">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="G86" s="1">
+        <v>11</v>
+      </c>
+      <c r="H86" s="1">
+        <v>2</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J86" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:10">
+      <c r="C87" s="1">
+        <v>82</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" s="3">
+        <v>5</v>
+      </c>
+      <c r="F87" s="1">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="G87" s="1">
+        <v>11</v>
+      </c>
+      <c r="H87" s="1">
+        <v>2</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J87" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:10">
+      <c r="C88" s="1">
+        <v>83</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E88" s="3">
+        <v>5</v>
+      </c>
+      <c r="F88" s="1">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="G88" s="1">
+        <v>11</v>
+      </c>
+      <c r="H88" s="1">
+        <v>2</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J88" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
+      <c r="C89" s="1">
+        <v>84</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5</v>
+      </c>
+      <c r="F89" s="1">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="G89" s="1">
+        <v>11</v>
+      </c>
+      <c r="H89" s="1">
+        <v>2</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J89" s="1">
+        <v>11</v>
+      </c>
+    </row>
     <row r="106" customHeight="1" spans="6:6">
       <c r="F106" s="7"/>
     </row>
